--- a/Excel/CatHeroDefense.xlsx
+++ b/Excel/CatHeroDefense.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NXP2\HDProject\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1A1CD6-AAC1-469F-A804-911B78A587DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="TestConstValue" sheetId="1" r:id="rId1"/>
-    <sheet name="GradeStat" sheetId="2" r:id="rId2"/>
-    <sheet name="SetBuff" sheetId="3" r:id="rId3"/>
-    <sheet name="UnitPropertyDefine" sheetId="4" r:id="rId4"/>
-    <sheet name="UnitTypeDefine" sheetId="5" r:id="rId5"/>
-    <sheet name="Ignore" sheetId="6" r:id="rId6"/>
+    <sheet name="TestConstValue" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="GradeStat" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="SetBuff" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="UnitPropertyDefine" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="UnitTypeDefine" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Ignore" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -32,245 +27,248 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
   <si>
-    <t>Seed</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>DevName</t>
-  </si>
-  <si>
-    <t>Val</t>
-  </si>
-  <si>
-    <t>Str</t>
-  </si>
-  <si>
-    <t>StartingGoodsType</t>
-  </si>
-  <si>
-    <t>시작 재화 종류</t>
-  </si>
-  <si>
-    <t>StartingGoodsPrice</t>
-  </si>
-  <si>
-    <t>시작 재화 지급 값</t>
-  </si>
-  <si>
-    <t>RollingDicePrice</t>
-  </si>
-  <si>
-    <t>주사위 굴리기 비용</t>
-  </si>
-  <si>
-    <t>Dicelock1Price</t>
-  </si>
-  <si>
-    <t>주사위 1개 잠금 비용</t>
-  </si>
-  <si>
-    <t>Dicelock2Price</t>
-  </si>
-  <si>
-    <t>주사위 2개 잠금 비용</t>
-  </si>
-  <si>
-    <t>MonsterRecallTime</t>
-  </si>
-  <si>
-    <t>다음 몬스터 소환 대기 시간(밀리초)</t>
-  </si>
-  <si>
-    <t>MonsterKillingReward</t>
-  </si>
-  <si>
-    <t>몬스터 처치 시 보상 값</t>
-  </si>
-  <si>
-    <t>BossMonsterKillingReward</t>
-  </si>
-  <si>
-    <t>보스 몬스터 처치 시 보상 값</t>
-  </si>
-  <si>
-    <t>MonsterWaveWaitTime</t>
-  </si>
-  <si>
-    <t>몬스터 웨이브 대기 시간(초)</t>
-  </si>
-  <si>
-    <t>RecyclePrice</t>
-  </si>
-  <si>
-    <t>돌려 받는 비용. 별 등급으로 곱함</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Vitality</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>BuffGroupSeed</t>
-  </si>
-  <si>
-    <t>IconName</t>
-  </si>
-  <si>
-    <t>Fire</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Wind</t>
-  </si>
-  <si>
-    <t>Archer</t>
-  </si>
-  <si>
-    <t>Mage</t>
-  </si>
-  <si>
-    <t>Lancer</t>
-  </si>
-  <si>
-    <t>Knight</t>
-  </si>
-  <si>
-    <t>Rogue</t>
-  </si>
-  <si>
-    <t>Gunslinger</t>
-  </si>
-  <si>
-    <t>Alchemist</t>
-  </si>
-  <si>
-    <t>Property</t>
-  </si>
-  <si>
-    <t>AdventageProperty</t>
-  </si>
-  <si>
-    <t>DisadventageProperty</t>
-  </si>
-  <si>
-    <t>AdventageScale</t>
-  </si>
-  <si>
-    <t>DisadventageScale</t>
-  </si>
-  <si>
-    <t>SpawnEffectAssetKey</t>
-  </si>
-  <si>
-    <t>OffsetY</t>
-  </si>
-  <si>
-    <t>Assets/GameResources/Effect/GFX_Mon_summon_Red.prefab</t>
-  </si>
-  <si>
-    <t>UI_BuffIcon_01</t>
-  </si>
-  <si>
-    <t>Assets/GameResources/Effect/GFX_Mon_summon_Blue.prefab</t>
-  </si>
-  <si>
-    <t>UI_BuffIcon_03</t>
-  </si>
-  <si>
-    <t>Assets/GameResources/Effect/GFX_Mon_summon_Green.prefab</t>
-  </si>
-  <si>
-    <t>UI_BuffIcon_02</t>
-  </si>
-  <si>
-    <t>UI_BuffIcon_06</t>
-  </si>
-  <si>
-    <t>Ninja</t>
-  </si>
-  <si>
-    <t>Warrior</t>
-  </si>
-  <si>
-    <t>UI_BuffIcon_04</t>
-  </si>
-  <si>
-    <t>DragonKnight</t>
-  </si>
-  <si>
-    <t>UI_BuffIcon_05</t>
-  </si>
-  <si>
-    <t>Summoner</t>
-  </si>
-  <si>
-    <t>CharacterType</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>궁수</t>
-  </si>
-  <si>
-    <t>마법사</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>버퍼</t>
-  </si>
-  <si>
-    <t>소환사</t>
-  </si>
-  <si>
-    <t>도적</t>
-  </si>
-  <si>
-    <t>닌자</t>
-  </si>
-  <si>
-    <t>연금술사</t>
-  </si>
-  <si>
-    <t>기사</t>
-  </si>
-  <si>
-    <t>전사</t>
-  </si>
-  <si>
-    <t>Dragon Knight</t>
-  </si>
-  <si>
-    <t>용기사</t>
-  </si>
-  <si>
-    <t>창기사</t>
-  </si>
-  <si>
-    <t>총잡이</t>
+    <t xml:space="preserve">Seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Str</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartingGoodsType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 재화 종류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StartingGoodsPrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작 재화 지급 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RollingDicePrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주사위 굴리기 비용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dicelock1Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주사위 1개 잠금 비용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dicelock2Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주사위 2개 잠금 비용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MonsterRecallTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다음 몬스터 소환 대기 시간(밀리초)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MonsterKillingReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">몬스터 처치 시 보상 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BossMonsterKillingReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보스 몬스터 처치 시 보상 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MonsterWaveWaitTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">몬스터 웨이브 대기 시간(초)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RecyclePrice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌려 받는 비용. 별 등급으로 곱함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuffGroupSeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IconName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunslinger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alchemist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AdventageProperty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DisadventageProperty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AdventageScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DisadventageScale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpawnEffectAssetKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OffsetY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/GameResources/Effect/GFX_Mon_summon_Red.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI_BuffIcon_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/GameResources/Effect/GFX_Mon_summon_Blue.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI_BuffIcon_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/GameResources/Effect/GFX_Mon_summon_Green.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI_BuffIcon_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI_BuffIcon_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warrior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI_BuffIcon_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DragonKnight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI_BuffIcon_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CharacterType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비고</t>
+  </si>
+  <si>
+    <t xml:space="preserve">궁수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마법사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버퍼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소환사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">닌자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연금술사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">용기사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">창기사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">총잡이</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,16 +278,28 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -301,20 +311,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79979857783745845"/>
+        <fgColor theme="4" tint="0.7998"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -329,46 +339,65 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -427,76 +456,60 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -528,7 +541,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -552,7 +565,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -612,28 +625,29 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="25.3984375" customWidth="1"/>
-    <col min="3" max="3" width="33.8984375" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="6" max="6" width="16.19921875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,594 +664,616 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0" t="n">
         <v>100100105</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C5">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6">
+      <c r="B5" s="0" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0" t="n">
         <v>2.6</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0" t="n">
         <v>2.9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="10.09765625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2">
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14">
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="0" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15">
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0" t="n">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20.3984375" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
-    <col min="5" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="56" customWidth="1"/>
-    <col min="8" max="8" width="14.19921875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="C2">
+      <c r="E2" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2">
+      <c r="C4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3">
-        <v>1.2</v>
-      </c>
-      <c r="C3">
-        <v>0.7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4">
-        <v>1.2</v>
-      </c>
-      <c r="C4">
-        <v>0.7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="H4" s="0" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;Kffffff페이지 &amp;P</oddFooter>
   </headerFooter>
@@ -1245,115 +1281,118 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.69921875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.4"/>
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;Kffffff페이지 &amp;P</oddFooter>
   </headerFooter>
@@ -1361,14 +1400,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="16.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>62</v>
       </c>
@@ -1379,7 +1421,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>35</v>
       </c>
@@ -1390,7 +1432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -1401,7 +1443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>66</v>
       </c>
@@ -1412,7 +1454,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1420,7 +1462,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
@@ -1428,7 +1470,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>56</v>
       </c>
@@ -1436,7 +1478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>41</v>
       </c>
@@ -1444,7 +1486,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
@@ -1452,7 +1494,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
@@ -1460,7 +1502,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>74</v>
       </c>
@@ -1468,7 +1510,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
@@ -1476,7 +1518,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -1485,14 +1527,18 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A10" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A2:A10" type="list">
       <formula1>$C$2:$C$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>